--- a/inventario_max_technology_store.xlsx
+++ b/inventario_max_technology_store.xlsx
@@ -6919,18 +6919,34 @@
       </c>
       <c r="B60" s="53" t="inlineStr">
         <is>
-          <t>Memoria Ddr4 8gb 2400t Samsung Portatil</t>
-        </is>
-      </c>
-      <c r="C60" s="54" t="inlineStr"/>
+          <t>Memoria RAM Samsung 8GB DDR4 2400MHz SODIMM para Portátil (PC4-2400T)</t>
+        </is>
+      </c>
+      <c r="C60" s="54" t="inlineStr">
+        <is>
+          <t>Almacenamiento y Memorias</t>
+        </is>
+      </c>
       <c r="D60" s="54" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="E60" s="55" t="inlineStr"/>
-      <c r="F60" s="55" t="inlineStr"/>
-      <c r="G60" s="55" t="inlineStr"/>
+      <c r="E60" s="55" t="inlineStr">
+        <is>
+          <t>M471A1K43CB1-CRC</t>
+        </is>
+      </c>
+      <c r="F60" s="55" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="G60" s="55" t="inlineStr">
+        <is>
+          <t>Sin código</t>
+        </is>
+      </c>
       <c r="H60" s="55" t="inlineStr">
         <is>
           <t>REMANUFACTURADO</t>
@@ -6983,7 +6999,7 @@
       </c>
       <c r="U60" s="55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Sin garantía</t>
         </is>
       </c>
       <c r="V60" s="54" t="inlineStr">
@@ -6991,8 +7007,22 @@
           <t>IMAGENES DE PRODUCTOS/DDR4_8GB_2400MHZ.webp</t>
         </is>
       </c>
-      <c r="W60" s="54" t="inlineStr"/>
-      <c r="X60" s="54" t="inlineStr"/>
+      <c r="W60" s="54" t="inlineStr">
+        <is>
+          <t>• Capacidad: 8 GB
+• Tipo: Memoria RAM DDR4 SODIMM para computadores portátiles / laptops
+• Frecuencia / Velocidad: 2400 MHz (PC4-2400T)
+• Formato: 260 pines SODIMM
+• Voltaje: 1.2V
+• Latencia: CL17
+• Ideal para repotenciar y acelerar portátiles de diversas marcas (HP, Lenovo, Dell, Asus, Acer).</t>
+        </is>
+      </c>
+      <c r="X60" s="54" t="inlineStr">
+        <is>
+          <t>100% testeada con MemTest86 en taller.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="63" t="n"/>

--- a/inventario_max_technology_store.xlsx
+++ b/inventario_max_technology_store.xlsx
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="J49" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" s="59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="55" t="inlineStr">
         <is>

--- a/inventario_max_technology_store.xlsx
+++ b/inventario_max_technology_store.xlsx
@@ -353,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -537,6 +537,39 @@
     </xf>
     <xf numFmtId="166" fontId="19" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3317,7 +3350,7 @@
         </is>
       </c>
       <c r="J25" s="58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="59" t="n">
         <v>1</v>
@@ -7025,22 +7058,99 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="63" t="n"/>
-      <c r="J61" s="63" t="n"/>
-      <c r="K61" s="63" t="n"/>
-      <c r="L61" s="64" t="n"/>
-      <c r="M61" s="65" t="n"/>
-      <c r="N61" s="64" t="n"/>
-      <c r="O61" s="65" t="n"/>
-      <c r="P61" s="64" t="n"/>
-      <c r="Q61" s="64" t="n"/>
-      <c r="R61" s="64" t="n"/>
-      <c r="S61" s="65" t="n"/>
-      <c r="T61" s="64" t="n"/>
-      <c r="U61" s="64" t="n"/>
-      <c r="V61" s="64" t="n"/>
-      <c r="W61" s="64" t="n"/>
-      <c r="X61" s="64" t="n"/>
+      <c r="A61" s="66" t="inlineStr">
+        <is>
+          <t>MTS-0058</t>
+        </is>
+      </c>
+      <c r="B61" s="67" t="inlineStr">
+        <is>
+          <t>Botella de Tinta Original Epson T504 Magenta</t>
+        </is>
+      </c>
+      <c r="C61" s="68" t="inlineStr">
+        <is>
+          <t>Tintas y Suministros</t>
+        </is>
+      </c>
+      <c r="D61" s="68" t="inlineStr">
+        <is>
+          <t>Epson</t>
+        </is>
+      </c>
+      <c r="E61" s="69" t="inlineStr">
+        <is>
+          <t>T504320-AL</t>
+        </is>
+      </c>
+      <c r="F61" s="69" t="inlineStr">
+        <is>
+          <t>Magenta</t>
+        </is>
+      </c>
+      <c r="G61" s="69" t="inlineStr"/>
+      <c r="H61" s="69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="I61" s="70" t="inlineStr">
+        <is>
+          <t>🟢 En Stock</t>
+        </is>
+      </c>
+      <c r="J61" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="72" t="inlineStr">
+        <is>
+          <t>Taller</t>
+        </is>
+      </c>
+      <c r="M61" s="73" t="n">
+        <v>20000</v>
+      </c>
+      <c r="N61" s="74" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="O61" s="75">
+        <f>IF(N61&lt;1, ROUNDUP(M61/(1-N61), -3), M61)</f>
+        <v/>
+      </c>
+      <c r="P61" s="74" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q61" s="73">
+        <f>IF((1-N61-P61)&gt;0, ROUNDUP((M61+IF(O61&gt;=90000,20000,0))/(1-N61-P61), -3), O61)</f>
+        <v/>
+      </c>
+      <c r="R61" s="73">
+        <f>O61</f>
+        <v/>
+      </c>
+      <c r="S61" s="73">
+        <f>O61-M61</f>
+        <v/>
+      </c>
+      <c r="T61" s="74">
+        <f>IF(O61&gt;0, (O61-M61)/O61, 0)</f>
+        <v/>
+      </c>
+      <c r="U61" s="72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V61" s="76" t="inlineStr">
+        <is>
+          <t>IMAGENES DE PRODUCTOS/t504302.jpg</t>
+        </is>
+      </c>
+      <c r="W61" s="76" t="inlineStr"/>
+      <c r="X61" s="76" t="inlineStr"/>
     </row>
     <row r="62"/>
     <row r="63"/>

--- a/inventario_max_technology_store.xlsx
+++ b/inventario_max_technology_store.xlsx
@@ -353,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -570,6 +570,18 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7152,8 +7164,184 @@
       <c r="W61" s="76" t="inlineStr"/>
       <c r="X61" s="76" t="inlineStr"/>
     </row>
-    <row r="62"/>
-    <row r="63"/>
+    <row r="62">
+      <c r="A62" s="77" t="inlineStr">
+        <is>
+          <t>MTS-0059</t>
+        </is>
+      </c>
+      <c r="B62" s="67" t="inlineStr">
+        <is>
+          <t>cale usb para impresora 1.5 Mtrs</t>
+        </is>
+      </c>
+      <c r="C62" s="68" t="inlineStr">
+        <is>
+          <t>Tintas y Suministros</t>
+        </is>
+      </c>
+      <c r="D62" s="68" t="inlineStr"/>
+      <c r="E62" s="69" t="inlineStr"/>
+      <c r="F62" s="69" t="inlineStr">
+        <is>
+          <t>gris</t>
+        </is>
+      </c>
+      <c r="G62" s="69" t="inlineStr">
+        <is>
+          <t>80182</t>
+        </is>
+      </c>
+      <c r="H62" s="69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="I62" s="70" t="inlineStr">
+        <is>
+          <t>🟢 En Stock</t>
+        </is>
+      </c>
+      <c r="J62" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="69" t="inlineStr">
+        <is>
+          <t>Taller</t>
+        </is>
+      </c>
+      <c r="M62" s="78" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N62" s="79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O62" s="80">
+        <f>IF(N62&lt;1, ROUNDUP(M62/(1-N62), -3), M62)</f>
+        <v/>
+      </c>
+      <c r="P62" s="79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q62" s="78">
+        <f>IF((1-N62-P62)&gt;0, ROUNDUP((M62+IF(O62&gt;=90000,20000,0))/(1-N62-P62), -3), O62)</f>
+        <v/>
+      </c>
+      <c r="R62" s="78">
+        <f>O62</f>
+        <v/>
+      </c>
+      <c r="S62" s="78">
+        <f>O62-M62</f>
+        <v/>
+      </c>
+      <c r="T62" s="79">
+        <f>IF(O62&gt;0, (O62-M62)/O62, 0)</f>
+        <v/>
+      </c>
+      <c r="U62" s="69" t="inlineStr">
+        <is>
+          <t>Garantía oficial</t>
+        </is>
+      </c>
+      <c r="V62" s="68" t="inlineStr">
+        <is>
+          <t>IMAGENES DE PRODUCTOS/cable_usb_para_impresora_1.5_mtrs.webp</t>
+        </is>
+      </c>
+      <c r="W62" s="68" t="inlineStr"/>
+      <c r="X62" s="68" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="77" t="inlineStr">
+        <is>
+          <t>MTS-0060</t>
+        </is>
+      </c>
+      <c r="B63" s="67" t="inlineStr">
+        <is>
+          <t>Hub USB 3.0 4 Puertos Follow Me</t>
+        </is>
+      </c>
+      <c r="C63" s="68" t="inlineStr">
+        <is>
+          <t>Tintas y Suministros</t>
+        </is>
+      </c>
+      <c r="D63" s="68" t="inlineStr">
+        <is>
+          <t>Follow me</t>
+        </is>
+      </c>
+      <c r="E63" s="69" t="inlineStr"/>
+      <c r="F63" s="69" t="inlineStr"/>
+      <c r="G63" s="69" t="inlineStr"/>
+      <c r="H63" s="69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="I63" s="70" t="inlineStr">
+        <is>
+          <t>🟢 En Stock</t>
+        </is>
+      </c>
+      <c r="J63" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="69" t="inlineStr">
+        <is>
+          <t>Taller</t>
+        </is>
+      </c>
+      <c r="M63" s="78" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N63" s="79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O63" s="80">
+        <f>IF(N63&lt;1, ROUNDUP(M63/(1-N63), -3), M63)</f>
+        <v/>
+      </c>
+      <c r="P63" s="79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q63" s="78">
+        <f>IF((1-N63-P63)&gt;0, ROUNDUP((M63+IF(O63&gt;=90000,20000,0))/(1-N63-P63), -3), O63)</f>
+        <v/>
+      </c>
+      <c r="R63" s="78">
+        <f>O63</f>
+        <v/>
+      </c>
+      <c r="S63" s="78">
+        <f>O63-M63</f>
+        <v/>
+      </c>
+      <c r="T63" s="79">
+        <f>IF(O63&gt;0, (O63-M63)/O63, 0)</f>
+        <v/>
+      </c>
+      <c r="U63" s="69" t="inlineStr">
+        <is>
+          <t>Garantía oficial</t>
+        </is>
+      </c>
+      <c r="V63" s="68" t="inlineStr">
+        <is>
+          <t>IMAGENES DE PRODUCTOS/Hub-USB-3-4-Puertos-FollowMe-3565-1.webp</t>
+        </is>
+      </c>
+      <c r="W63" s="68" t="inlineStr"/>
+      <c r="X63" s="68" t="inlineStr"/>
+    </row>
     <row r="64"/>
     <row r="65"/>
     <row r="66"/>

--- a/inventario_max_technology_store.xlsx
+++ b/inventario_max_technology_store.xlsx
@@ -4912,7 +4912,7 @@
       </c>
       <c r="B40" s="53" t="inlineStr">
         <is>
-          <t>Monitor Dahua 27" Panel IPS 144Hz 1ms Full HD</t>
+          <t>Monitor Dahua LED 27 Pulgadas FHD 144Hz 1ms IPS (DHI-LM27-A221Y)</t>
         </is>
       </c>
       <c r="C40" s="54" t="inlineStr">
@@ -4930,7 +4930,11 @@
           <t>DHI-LM27-A221Y</t>
         </is>
       </c>
-      <c r="F40" s="55" t="inlineStr"/>
+      <c r="F40" s="55" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
       <c r="G40" s="56" t="inlineStr">
         <is>
           <t>6938596001279</t>
@@ -4938,30 +4942,30 @@
       </c>
       <c r="H40" s="55" t="inlineStr">
         <is>
-          <t>Nuevo</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="I40" s="57" t="inlineStr">
         <is>
-          <t>⚪ Agotado</t>
+          <t>🟢 En Stock</t>
         </is>
       </c>
       <c r="J40" s="58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K40" s="59" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L40" s="55" t="inlineStr">
         <is>
-          <t>Estante B - Nivel 1</t>
+          <t>Bodega / Taller - Estante Monitores</t>
         </is>
       </c>
       <c r="M40" s="60" t="n">
-        <v>327513</v>
+        <v>311071</v>
       </c>
       <c r="N40" s="61" t="n">
-        <v>0.25</v>
+        <v>0.20238</v>
       </c>
       <c r="O40" s="62">
         <f>IF(N40&lt;1, ROUNDUP(M40/(1-N40), -3), M40)</f>
@@ -4993,17 +4997,23 @@
       </c>
       <c r="V40" s="54" t="inlineStr">
         <is>
-          <t>identidad visual max tech/Logo MAX Tech.png</t>
+          <t>IMAGENES DE PRODUCTOS/Monitor dahua led 27 pulgadas ips 144 hz full hd.webp</t>
         </is>
       </c>
       <c r="W40" s="54" t="inlineStr">
         <is>
-          <t>Monitor grande de 27 pulgadas Full HD con panel IPS a 144Hz. Brinda un espacio de trabajo amplio y descansado para tener varias ventanas abiertas al tiempo, ver videos o jugar con máxima fluidez. Tiene marco ultradelgado, puertos HDMI y VGA, y 3 años de garantía.</t>
+          <t>• Pantalla: 27 Pulgadas Full HD (1920 x 1080) antirreflejo
+• Panel: IPS con ángulos de visión amplios de 178°
+• Tasa de refresco: 144 Hz ultrarrápida
+• Tiempo de respuesta: 1 ms
+• Conectividad: Puertos HDMI y VGA
+• Diseño: Biseles ultradelgados con base plástica resistente
+• Garantía oficial de 3 años Dahua.</t>
         </is>
       </c>
       <c r="X40" s="54" t="inlineStr">
         <is>
-          <t>Gran formato de 27 pulgadas.</t>
+          <t>10 unidades físicas selladas. Seriales: BLR01916302500002 a BLR01916302500646. Factura FT-9364.</t>
         </is>
       </c>
     </row>
@@ -7342,8 +7352,229 @@
       <c r="W63" s="68" t="inlineStr"/>
       <c r="X63" s="68" t="inlineStr"/>
     </row>
-    <row r="64"/>
-    <row r="65"/>
+    <row r="64">
+      <c r="A64" s="77" t="inlineStr">
+        <is>
+          <t>MTS-0061</t>
+        </is>
+      </c>
+      <c r="B64" s="67" t="inlineStr">
+        <is>
+          <t>Disco Estado Sólido SSD M.2 NVMe 1TB ADATA Legend 710 PCIe Gen3 x4</t>
+        </is>
+      </c>
+      <c r="C64" s="68" t="inlineStr">
+        <is>
+          <t>Almacenamiento y Memorias</t>
+        </is>
+      </c>
+      <c r="D64" s="68" t="inlineStr">
+        <is>
+          <t>ADATA</t>
+        </is>
+      </c>
+      <c r="E64" s="69" t="inlineStr">
+        <is>
+          <t>ALEG-710-1TCS</t>
+        </is>
+      </c>
+      <c r="F64" s="69" t="inlineStr">
+        <is>
+          <t>Azul / Negro</t>
+        </is>
+      </c>
+      <c r="G64" s="69" t="inlineStr">
+        <is>
+          <t>4711085635398</t>
+        </is>
+      </c>
+      <c r="H64" s="69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="I64" s="70" t="inlineStr">
+        <is>
+          <t>🟢 En Stock</t>
+        </is>
+      </c>
+      <c r="J64" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" s="69" t="inlineStr">
+        <is>
+          <t>Vitrina Accesorios / Taller</t>
+        </is>
+      </c>
+      <c r="M64" s="78" t="n">
+        <v>530000</v>
+      </c>
+      <c r="N64" s="79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O64" s="80">
+        <f>IF(N64&lt;1, ROUNDUP(M64/(1-N64), -3), M64)</f>
+        <v/>
+      </c>
+      <c r="P64" s="79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q64" s="78">
+        <f>IF((1-N64-P64)&gt;0, ROUNDUP((M64+IF(O64&gt;=90000,20000,0))/(1-N64-P64), -3), O64)</f>
+        <v/>
+      </c>
+      <c r="R64" s="78">
+        <f>O64</f>
+        <v/>
+      </c>
+      <c r="S64" s="78">
+        <f>O64-M64</f>
+        <v/>
+      </c>
+      <c r="T64" s="79">
+        <f>IF(O64&gt;0, (O64-M64)/O64, 0)</f>
+        <v/>
+      </c>
+      <c r="U64" s="69" t="inlineStr">
+        <is>
+          <t>6 Meses</t>
+        </is>
+      </c>
+      <c r="V64" s="68" t="inlineStr">
+        <is>
+          <t>IMAGENES DE PRODUCTOS/ADATA_LEGEND_710_1TB.jpg</t>
+        </is>
+      </c>
+      <c r="W64" s="68" t="inlineStr">
+        <is>
+          <t>• Capacidad: 1 TB (1000 GB)
+• Formato: M.2 2280
+• Interfaz: PCIe Gen3 x4 NVMe 1.4
+• Velocidad de lectura secuencial: Hasta 2.400 MB/s
+• Velocidad de escritura secuencial: Hasta 1.800 MB/s
+• Disipador térmico de aluminio incluido (reduce temperatura hasta 15%)
+• Compatible con PCs de escritorio y portátiles con slot M.2 NVMe.</t>
+        </is>
+      </c>
+      <c r="X64" s="68" t="inlineStr">
+        <is>
+          <t>2 unidades físicas. Seriales: 4P2220413136, 4P2220410141. Facturas FEVO 33176 y 33181.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="77" t="inlineStr">
+        <is>
+          <t>MTS-0062</t>
+        </is>
+      </c>
+      <c r="B65" s="67" t="inlineStr">
+        <is>
+          <t>Teclado para Portátil Acer Aspire E1-470 E5-471P V3-472 3830T 4830 Negro Español</t>
+        </is>
+      </c>
+      <c r="C65" s="68" t="inlineStr">
+        <is>
+          <t>Periféricos y Accesorios</t>
+        </is>
+      </c>
+      <c r="D65" s="68" t="inlineStr">
+        <is>
+          <t>Acer / Compatible</t>
+        </is>
+      </c>
+      <c r="E65" s="69" t="inlineStr">
+        <is>
+          <t>00002272</t>
+        </is>
+      </c>
+      <c r="F65" s="69" t="inlineStr">
+        <is>
+          <t>Negro</t>
+        </is>
+      </c>
+      <c r="G65" s="69" t="inlineStr">
+        <is>
+          <t>Sin código</t>
+        </is>
+      </c>
+      <c r="H65" s="69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="I65" s="70" t="inlineStr">
+        <is>
+          <t>🟢 En Stock</t>
+        </is>
+      </c>
+      <c r="J65" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="69" t="inlineStr">
+        <is>
+          <t>Taller - Repuestos</t>
+        </is>
+      </c>
+      <c r="M65" s="78" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N65" s="79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O65" s="80">
+        <f>IF(N65&lt;1, ROUNDUP(M65/(1-N65), -3), M65)</f>
+        <v/>
+      </c>
+      <c r="P65" s="79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q65" s="78">
+        <f>IF((1-N65-P65)&gt;0, ROUNDUP((M65+IF(O65&gt;=90000,20000,0))/(1-N65-P65), -3), O65)</f>
+        <v/>
+      </c>
+      <c r="R65" s="78">
+        <f>O65</f>
+        <v/>
+      </c>
+      <c r="S65" s="78">
+        <f>O65-M65</f>
+        <v/>
+      </c>
+      <c r="T65" s="79">
+        <f>IF(O65&gt;0, (O65-M65)/O65, 0)</f>
+        <v/>
+      </c>
+      <c r="U65" s="69" t="inlineStr">
+        <is>
+          <t>6 Meses</t>
+        </is>
+      </c>
+      <c r="V65" s="68" t="inlineStr">
+        <is>
+          <t>identidad visual max tech/Logo MAX Tech.png</t>
+        </is>
+      </c>
+      <c r="W65" s="68" t="inlineStr">
+        <is>
+          <t>• Idioma / Distribución: Español con letra Ñ
+• Color: Negro mate
+• Compatibilidad: Acer Aspire E1-470, E1-470G, E1-472, E5-471, E5-471P, V3-472, 3830, 3830T, 4830, 4830T
+• Tipo de repuesto: Teclado de reemplazo de alta respuesta táctil.</t>
+        </is>
+      </c>
+      <c r="X65" s="68" t="inlineStr">
+        <is>
+          <t>Serial: 2F50031050103. Factura FEVO 33009.</t>
+        </is>
+      </c>
+    </row>
     <row r="66"/>
     <row r="67"/>
     <row r="68"/>

--- a/inventario_max_technology_store.xlsx
+++ b/inventario_max_technology_store.xlsx
@@ -7413,7 +7413,7 @@
         <v>530000</v>
       </c>
       <c r="N64" s="79" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="O64" s="80">
         <f>IF(N64&lt;1, ROUNDUP(M64/(1-N64), -3), M64)</f>
@@ -7459,11 +7459,7 @@
 • Compatible con PCs de escritorio y portátiles con slot M.2 NVMe.</t>
         </is>
       </c>
-      <c r="X64" s="68" t="inlineStr">
-        <is>
-          <t>2 unidades físicas. Seriales: 4P2220413136, 4P2220410141. Facturas FEVO 33176 y 33181.</t>
-        </is>
-      </c>
+      <c r="X64" s="68" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="77" t="inlineStr">
